--- a/Projects/Cade-Cunningham.xlsx
+++ b/Projects/Cade-Cunningham.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012C2FE3-2FE3-5941-90CB-6A58411CD563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C2E564-1A0A-3542-8502-067C6EDF89BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="11" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
